--- a/artfynd/A 46081-2025 artfynd.xlsx
+++ b/artfynd/A 46081-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AY31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1999,6 +1999,1801 @@
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>129744133</v>
+      </c>
+      <c r="B15" t="n">
+        <v>57735</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Lappberget, Mpd</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>601222</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6959449</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Timrå</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Ljustorp</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>129743173</v>
+      </c>
+      <c r="B16" t="n">
+        <v>57576</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>102621</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Sparvuggla</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Glaucidium passerinum</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Lappberget, Mpd</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>601219</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6959648</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Timrå</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Ljustorp</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>129745703</v>
+      </c>
+      <c r="B17" t="n">
+        <v>57735</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Alderbackberget, Mpd</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>601258</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6959417</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Timrå</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Ljustorp</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>129745723</v>
+      </c>
+      <c r="B18" t="n">
+        <v>57735</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Alderbackberget, Mpd</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>601272</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6959413</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Timrå</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Ljustorp</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>129744878</v>
+      </c>
+      <c r="B19" t="n">
+        <v>57735</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Alderbackberget, Mpd</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>601263</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6959271</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Timrå</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Ljustorp</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>129744814</v>
+      </c>
+      <c r="B20" t="n">
+        <v>57735</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Alderbackberget, Mpd</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>601247</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6959312</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Timrå</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Ljustorp</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>129745588</v>
+      </c>
+      <c r="B21" t="n">
+        <v>57735</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Alderbackberget, Mpd</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>601286</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6959377</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Timrå</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Ljustorp</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>129744699</v>
+      </c>
+      <c r="B22" t="n">
+        <v>57895</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Alderbackberget, Mpd</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>601189</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6959263</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Timrå</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Ljustorp</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>129744201</v>
+      </c>
+      <c r="B23" t="n">
+        <v>57735</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Lappberget, Mpd</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>601224</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6959429</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Timrå</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Ljustorp</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>129744421</v>
+      </c>
+      <c r="B24" t="n">
+        <v>57735</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Alderbackberget, Mpd</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>601240</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6959385</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Timrå</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Ljustorp</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>129745773</v>
+      </c>
+      <c r="B25" t="n">
+        <v>57735</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Alderbackberget, Mpd</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>601280</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6959438</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Timrå</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Ljustorp</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>129744312</v>
+      </c>
+      <c r="B26" t="n">
+        <v>57735</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Alderbackberget, Mpd</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>601225</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6959403</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Timrå</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Ljustorp</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>129743807</v>
+      </c>
+      <c r="B27" t="n">
+        <v>78833</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Lappberget, Mpd</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>601219</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6959554</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Timrå</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Ljustorp</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>129744479</v>
+      </c>
+      <c r="B28" t="n">
+        <v>57895</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Alderbackberget, Mpd</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>601226</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6959363</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Timrå</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Ljustorp</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>129742961</v>
+      </c>
+      <c r="B29" t="n">
+        <v>57735</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Lappberget, Mpd</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>601187</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6959691</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Timrå</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Ljustorp</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>129744685</v>
+      </c>
+      <c r="B30" t="n">
+        <v>98768</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Alderbackberget, Mpd</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>601189</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6959263</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Timrå</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Ljustorp</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>129743133</v>
+      </c>
+      <c r="B31" t="n">
+        <v>57735</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Lappberget, Mpd</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>601237</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6959656</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Timrå</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Ljustorp</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 46081-2025 artfynd.xlsx
+++ b/artfynd/A 46081-2025 artfynd.xlsx
@@ -2001,27 +2001,27 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129744133</v>
+        <v>129743173</v>
       </c>
       <c r="B15" t="n">
-        <v>57735</v>
+        <v>57577</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>102621</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2029,10 +2029,14 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2041,10 +2045,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>601222</v>
+        <v>601219</v>
       </c>
       <c r="R15" t="n">
-        <v>6959449</v>
+        <v>6959648</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2077,11 +2081,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-11-18</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2108,54 +2107,54 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129743173</v>
+        <v>129744699</v>
       </c>
       <c r="B16" t="n">
-        <v>57576</v>
+        <v>57896</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>102621</v>
+        <v>103021</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Lappberget, Mpd</t>
+          <t>Alderbackberget, Mpd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>601219</v>
+        <v>601189</v>
       </c>
       <c r="R16" t="n">
-        <v>6959648</v>
+        <v>6959263</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2214,10 +2213,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129745703</v>
+        <v>129743807</v>
       </c>
       <c r="B17" t="n">
-        <v>57735</v>
+        <v>78834</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2225,39 +2224,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Alderbackberget, Mpd</t>
+          <t>Lappberget, Mpd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>601258</v>
+        <v>601219</v>
       </c>
       <c r="R17" t="n">
-        <v>6959417</v>
+        <v>6959554</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2290,11 +2284,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-11-18</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2321,10 +2310,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129745723</v>
+        <v>129744479</v>
       </c>
       <c r="B18" t="n">
-        <v>57735</v>
+        <v>57896</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2332,27 +2321,27 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2361,10 +2350,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>601272</v>
+        <v>601226</v>
       </c>
       <c r="R18" t="n">
-        <v>6959413</v>
+        <v>6959363</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2397,11 +2386,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-11-18</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2428,38 +2412,37 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129744878</v>
+        <v>129744685</v>
       </c>
       <c r="B19" t="n">
-        <v>57735</v>
+        <v>98769</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>50</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2468,10 +2451,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>601263</v>
+        <v>601189</v>
       </c>
       <c r="R19" t="n">
-        <v>6959271</v>
+        <v>6959263</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2504,11 +2487,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-11-18</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2535,10 +2513,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129744814</v>
+        <v>129744133</v>
       </c>
       <c r="B20" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2571,14 +2549,14 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Alderbackberget, Mpd</t>
+          <t>Lappberget, Mpd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>601247</v>
+        <v>601222</v>
       </c>
       <c r="R20" t="n">
-        <v>6959312</v>
+        <v>6959449</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2642,10 +2620,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129745588</v>
+        <v>129745703</v>
       </c>
       <c r="B21" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2673,7 +2651,7 @@
       <c r="I21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2682,10 +2660,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>601286</v>
+        <v>601258</v>
       </c>
       <c r="R21" t="n">
-        <v>6959377</v>
+        <v>6959417</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2749,10 +2727,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129744699</v>
+        <v>129745723</v>
       </c>
       <c r="B22" t="n">
-        <v>57895</v>
+        <v>57736</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2760,31 +2738,27 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -2793,10 +2767,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>601189</v>
+        <v>601272</v>
       </c>
       <c r="R22" t="n">
-        <v>6959263</v>
+        <v>6959413</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2829,6 +2803,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2855,10 +2834,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129744201</v>
+        <v>129745588</v>
       </c>
       <c r="B23" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2886,19 +2865,19 @@
       <c r="I23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Lappberget, Mpd</t>
+          <t>Alderbackberget, Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>601224</v>
+        <v>601286</v>
       </c>
       <c r="R23" t="n">
-        <v>6959429</v>
+        <v>6959377</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2962,10 +2941,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129744421</v>
+        <v>129744814</v>
       </c>
       <c r="B24" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2993,7 +2972,7 @@
       <c r="I24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3002,10 +2981,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>601240</v>
+        <v>601247</v>
       </c>
       <c r="R24" t="n">
-        <v>6959385</v>
+        <v>6959312</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3042,7 +3021,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3069,10 +3048,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129745773</v>
+        <v>129744878</v>
       </c>
       <c r="B25" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3109,10 +3088,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>601280</v>
+        <v>601263</v>
       </c>
       <c r="R25" t="n">
-        <v>6959438</v>
+        <v>6959271</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3176,10 +3155,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129744312</v>
+        <v>129744201</v>
       </c>
       <c r="B26" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3212,14 +3191,14 @@
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Alderbackberget, Mpd</t>
+          <t>Lappberget, Mpd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>601225</v>
+        <v>601224</v>
       </c>
       <c r="R26" t="n">
-        <v>6959403</v>
+        <v>6959429</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3283,10 +3262,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129743807</v>
+        <v>129745773</v>
       </c>
       <c r="B27" t="n">
-        <v>78833</v>
+        <v>57736</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3294,34 +3273,39 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Lappberget, Mpd</t>
+          <t>Alderbackberget, Mpd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>601219</v>
+        <v>601280</v>
       </c>
       <c r="R27" t="n">
-        <v>6959554</v>
+        <v>6959438</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3354,6 +3338,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3380,10 +3369,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129744479</v>
+        <v>129744421</v>
       </c>
       <c r="B28" t="n">
-        <v>57895</v>
+        <v>57736</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3391,27 +3380,27 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -3420,10 +3409,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>601226</v>
+        <v>601240</v>
       </c>
       <c r="R28" t="n">
-        <v>6959363</v>
+        <v>6959385</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3456,6 +3445,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3482,10 +3476,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129742961</v>
+        <v>129744312</v>
       </c>
       <c r="B29" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3513,19 +3507,19 @@
       <c r="I29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Lappberget, Mpd</t>
+          <t>Alderbackberget, Mpd</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>601187</v>
+        <v>601225</v>
       </c>
       <c r="R29" t="n">
-        <v>6959691</v>
+        <v>6959403</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3589,49 +3583,50 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129744685</v>
+        <v>129742961</v>
       </c>
       <c r="B30" t="n">
-        <v>98768</v>
+        <v>57736</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>50</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Alderbackberget, Mpd</t>
+          <t>Lappberget, Mpd</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>601189</v>
+        <v>601187</v>
       </c>
       <c r="R30" t="n">
-        <v>6959263</v>
+        <v>6959691</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3664,6 +3659,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3693,7 +3693,7 @@
         <v>129743133</v>
       </c>
       <c r="B31" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>

--- a/artfynd/A 46081-2025 artfynd.xlsx
+++ b/artfynd/A 46081-2025 artfynd.xlsx
@@ -2216,7 +2216,7 @@
         <v>129743807</v>
       </c>
       <c r="B17" t="n">
-        <v>78834</v>
+        <v>78839</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2415,7 +2415,7 @@
         <v>129744685</v>
       </c>
       <c r="B19" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 46081-2025 artfynd.xlsx
+++ b/artfynd/A 46081-2025 artfynd.xlsx
@@ -3262,7 +3262,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129745773</v>
+        <v>129744421</v>
       </c>
       <c r="B27" t="n">
         <v>57736</v>
@@ -3293,7 +3293,7 @@
       <c r="I27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -3302,10 +3302,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>601280</v>
+        <v>601240</v>
       </c>
       <c r="R27" t="n">
-        <v>6959438</v>
+        <v>6959385</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3369,7 +3369,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129744421</v>
+        <v>129744312</v>
       </c>
       <c r="B28" t="n">
         <v>57736</v>
@@ -3400,7 +3400,7 @@
       <c r="I28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -3409,10 +3409,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>601240</v>
+        <v>601225</v>
       </c>
       <c r="R28" t="n">
-        <v>6959385</v>
+        <v>6959403</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3449,7 +3449,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3476,7 +3476,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129744312</v>
+        <v>129745773</v>
       </c>
       <c r="B29" t="n">
         <v>57736</v>
@@ -3516,10 +3516,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>601225</v>
+        <v>601280</v>
       </c>
       <c r="R29" t="n">
-        <v>6959403</v>
+        <v>6959438</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>

--- a/artfynd/A 46081-2025 artfynd.xlsx
+++ b/artfynd/A 46081-2025 artfynd.xlsx
@@ -2727,7 +2727,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129745723</v>
+        <v>129745588</v>
       </c>
       <c r="B22" t="n">
         <v>57736</v>
@@ -2758,7 +2758,7 @@
       <c r="I22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -2767,10 +2767,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>601272</v>
+        <v>601286</v>
       </c>
       <c r="R22" t="n">
-        <v>6959413</v>
+        <v>6959377</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2834,7 +2834,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129745588</v>
+        <v>129744814</v>
       </c>
       <c r="B23" t="n">
         <v>57736</v>
@@ -2865,7 +2865,7 @@
       <c r="I23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -2874,10 +2874,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>601286</v>
+        <v>601247</v>
       </c>
       <c r="R23" t="n">
-        <v>6959377</v>
+        <v>6959312</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2941,7 +2941,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129744814</v>
+        <v>129745723</v>
       </c>
       <c r="B24" t="n">
         <v>57736</v>
@@ -2981,10 +2981,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>601247</v>
+        <v>601272</v>
       </c>
       <c r="R24" t="n">
-        <v>6959312</v>
+        <v>6959413</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3369,7 +3369,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129744312</v>
+        <v>129745773</v>
       </c>
       <c r="B28" t="n">
         <v>57736</v>
@@ -3409,10 +3409,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>601225</v>
+        <v>601280</v>
       </c>
       <c r="R28" t="n">
-        <v>6959403</v>
+        <v>6959438</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3476,7 +3476,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129745773</v>
+        <v>129744312</v>
       </c>
       <c r="B29" t="n">
         <v>57736</v>
@@ -3516,10 +3516,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>601280</v>
+        <v>601225</v>
       </c>
       <c r="R29" t="n">
-        <v>6959438</v>
+        <v>6959403</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>

--- a/artfynd/A 46081-2025 artfynd.xlsx
+++ b/artfynd/A 46081-2025 artfynd.xlsx
@@ -2727,7 +2727,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129745588</v>
+        <v>129745723</v>
       </c>
       <c r="B22" t="n">
         <v>57736</v>
@@ -2758,7 +2758,7 @@
       <c r="I22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -2767,10 +2767,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>601286</v>
+        <v>601272</v>
       </c>
       <c r="R22" t="n">
-        <v>6959377</v>
+        <v>6959413</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2834,7 +2834,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129744814</v>
+        <v>129745588</v>
       </c>
       <c r="B23" t="n">
         <v>57736</v>
@@ -2865,7 +2865,7 @@
       <c r="I23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -2874,10 +2874,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>601247</v>
+        <v>601286</v>
       </c>
       <c r="R23" t="n">
-        <v>6959312</v>
+        <v>6959377</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2941,7 +2941,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129745723</v>
+        <v>129744814</v>
       </c>
       <c r="B24" t="n">
         <v>57736</v>
@@ -2981,10 +2981,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>601272</v>
+        <v>601247</v>
       </c>
       <c r="R24" t="n">
-        <v>6959413</v>
+        <v>6959312</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3262,7 +3262,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129744421</v>
+        <v>129745773</v>
       </c>
       <c r="B27" t="n">
         <v>57736</v>
@@ -3293,7 +3293,7 @@
       <c r="I27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -3302,10 +3302,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>601240</v>
+        <v>601280</v>
       </c>
       <c r="R27" t="n">
-        <v>6959385</v>
+        <v>6959438</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3369,7 +3369,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129745773</v>
+        <v>129744421</v>
       </c>
       <c r="B28" t="n">
         <v>57736</v>
@@ -3400,7 +3400,7 @@
       <c r="I28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -3409,10 +3409,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>601280</v>
+        <v>601240</v>
       </c>
       <c r="R28" t="n">
-        <v>6959438</v>
+        <v>6959385</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3449,7 +3449,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD28" t="b">

--- a/artfynd/A 46081-2025 artfynd.xlsx
+++ b/artfynd/A 46081-2025 artfynd.xlsx
@@ -2415,7 +2415,7 @@
         <v>129744685</v>
       </c>
       <c r="B19" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2834,7 +2834,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129745588</v>
+        <v>129744878</v>
       </c>
       <c r="B23" t="n">
         <v>57736</v>
@@ -2865,7 +2865,7 @@
       <c r="I23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -2874,10 +2874,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>601286</v>
+        <v>601263</v>
       </c>
       <c r="R23" t="n">
-        <v>6959377</v>
+        <v>6959271</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3048,7 +3048,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129744878</v>
+        <v>129745588</v>
       </c>
       <c r="B25" t="n">
         <v>57736</v>
@@ -3079,7 +3079,7 @@
       <c r="I25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3088,10 +3088,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>601263</v>
+        <v>601286</v>
       </c>
       <c r="R25" t="n">
-        <v>6959271</v>
+        <v>6959377</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3262,7 +3262,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129745773</v>
+        <v>129744421</v>
       </c>
       <c r="B27" t="n">
         <v>57736</v>
@@ -3293,7 +3293,7 @@
       <c r="I27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -3302,10 +3302,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>601280</v>
+        <v>601240</v>
       </c>
       <c r="R27" t="n">
-        <v>6959438</v>
+        <v>6959385</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3369,7 +3369,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129744421</v>
+        <v>129745773</v>
       </c>
       <c r="B28" t="n">
         <v>57736</v>
@@ -3400,7 +3400,7 @@
       <c r="I28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -3409,10 +3409,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>601240</v>
+        <v>601280</v>
       </c>
       <c r="R28" t="n">
-        <v>6959385</v>
+        <v>6959438</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3449,7 +3449,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD28" t="b">

--- a/artfynd/A 46081-2025 artfynd.xlsx
+++ b/artfynd/A 46081-2025 artfynd.xlsx
@@ -2415,7 +2415,7 @@
         <v>129744685</v>
       </c>
       <c r="B19" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2834,7 +2834,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129744878</v>
+        <v>129745588</v>
       </c>
       <c r="B23" t="n">
         <v>57736</v>
@@ -2865,7 +2865,7 @@
       <c r="I23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -2874,10 +2874,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>601263</v>
+        <v>601286</v>
       </c>
       <c r="R23" t="n">
-        <v>6959271</v>
+        <v>6959377</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3048,7 +3048,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129745588</v>
+        <v>129744878</v>
       </c>
       <c r="B25" t="n">
         <v>57736</v>
@@ -3079,7 +3079,7 @@
       <c r="I25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3088,10 +3088,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>601286</v>
+        <v>601263</v>
       </c>
       <c r="R25" t="n">
-        <v>6959377</v>
+        <v>6959271</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3262,7 +3262,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129744421</v>
+        <v>129745773</v>
       </c>
       <c r="B27" t="n">
         <v>57736</v>
@@ -3293,7 +3293,7 @@
       <c r="I27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -3302,10 +3302,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>601240</v>
+        <v>601280</v>
       </c>
       <c r="R27" t="n">
-        <v>6959385</v>
+        <v>6959438</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3369,7 +3369,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129745773</v>
+        <v>129744421</v>
       </c>
       <c r="B28" t="n">
         <v>57736</v>
@@ -3400,7 +3400,7 @@
       <c r="I28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -3409,10 +3409,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>601280</v>
+        <v>601240</v>
       </c>
       <c r="R28" t="n">
-        <v>6959438</v>
+        <v>6959385</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3449,7 +3449,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD28" t="b">

--- a/artfynd/A 46081-2025 artfynd.xlsx
+++ b/artfynd/A 46081-2025 artfynd.xlsx
@@ -2415,7 +2415,7 @@
         <v>129744685</v>
       </c>
       <c r="B19" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2727,7 +2727,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129745723</v>
+        <v>129744814</v>
       </c>
       <c r="B22" t="n">
         <v>57736</v>
@@ -2767,10 +2767,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>601272</v>
+        <v>601247</v>
       </c>
       <c r="R22" t="n">
-        <v>6959413</v>
+        <v>6959312</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2834,7 +2834,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129745588</v>
+        <v>129745723</v>
       </c>
       <c r="B23" t="n">
         <v>57736</v>
@@ -2865,7 +2865,7 @@
       <c r="I23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -2874,10 +2874,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>601286</v>
+        <v>601272</v>
       </c>
       <c r="R23" t="n">
-        <v>6959377</v>
+        <v>6959413</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2941,7 +2941,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129744814</v>
+        <v>129745588</v>
       </c>
       <c r="B24" t="n">
         <v>57736</v>
@@ -2972,7 +2972,7 @@
       <c r="I24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -2981,10 +2981,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>601247</v>
+        <v>601286</v>
       </c>
       <c r="R24" t="n">
-        <v>6959312</v>
+        <v>6959377</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>

--- a/artfynd/A 46081-2025 artfynd.xlsx
+++ b/artfynd/A 46081-2025 artfynd.xlsx
@@ -2004,7 +2004,7 @@
         <v>129743173</v>
       </c>
       <c r="B15" t="n">
-        <v>57577</v>
+        <v>57578</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2110,7 +2110,7 @@
         <v>129744699</v>
       </c>
       <c r="B16" t="n">
-        <v>57896</v>
+        <v>57895</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2216,7 +2216,7 @@
         <v>129743807</v>
       </c>
       <c r="B17" t="n">
-        <v>78839</v>
+        <v>78842</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2313,7 +2313,7 @@
         <v>129744479</v>
       </c>
       <c r="B18" t="n">
-        <v>57896</v>
+        <v>57895</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2415,7 +2415,7 @@
         <v>129744685</v>
       </c>
       <c r="B19" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2516,7 +2516,7 @@
         <v>129744133</v>
       </c>
       <c r="B20" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2623,7 +2623,7 @@
         <v>129745703</v>
       </c>
       <c r="B21" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2727,10 +2727,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129744814</v>
+        <v>129745723</v>
       </c>
       <c r="B22" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2767,10 +2767,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>601247</v>
+        <v>601272</v>
       </c>
       <c r="R22" t="n">
-        <v>6959312</v>
+        <v>6959413</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2834,10 +2834,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129745723</v>
+        <v>129744878</v>
       </c>
       <c r="B23" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2874,10 +2874,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>601272</v>
+        <v>601263</v>
       </c>
       <c r="R23" t="n">
-        <v>6959413</v>
+        <v>6959271</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2941,10 +2941,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129745588</v>
+        <v>129744814</v>
       </c>
       <c r="B24" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2972,7 +2972,7 @@
       <c r="I24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -2981,10 +2981,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>601286</v>
+        <v>601247</v>
       </c>
       <c r="R24" t="n">
-        <v>6959377</v>
+        <v>6959312</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3048,10 +3048,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129744878</v>
+        <v>129745588</v>
       </c>
       <c r="B25" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3079,7 +3079,7 @@
       <c r="I25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3088,10 +3088,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>601263</v>
+        <v>601286</v>
       </c>
       <c r="R25" t="n">
-        <v>6959271</v>
+        <v>6959377</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3158,7 +3158,7 @@
         <v>129744201</v>
       </c>
       <c r="B26" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3265,7 +3265,7 @@
         <v>129744421</v>
       </c>
       <c r="B27" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3369,10 +3369,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129744312</v>
+        <v>129745773</v>
       </c>
       <c r="B28" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3409,10 +3409,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>601225</v>
+        <v>601280</v>
       </c>
       <c r="R28" t="n">
-        <v>6959403</v>
+        <v>6959438</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3476,10 +3476,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129745773</v>
+        <v>129744312</v>
       </c>
       <c r="B29" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3516,10 +3516,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>601280</v>
+        <v>601225</v>
       </c>
       <c r="R29" t="n">
-        <v>6959438</v>
+        <v>6959403</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3586,7 +3586,7 @@
         <v>129742961</v>
       </c>
       <c r="B30" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3693,7 +3693,7 @@
         <v>129743133</v>
       </c>
       <c r="B31" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>

--- a/artfynd/A 46081-2025 artfynd.xlsx
+++ b/artfynd/A 46081-2025 artfynd.xlsx
@@ -2727,7 +2727,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129745723</v>
+        <v>129745588</v>
       </c>
       <c r="B22" t="n">
         <v>57737</v>
@@ -2758,7 +2758,7 @@
       <c r="I22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -2767,10 +2767,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>601272</v>
+        <v>601286</v>
       </c>
       <c r="R22" t="n">
-        <v>6959413</v>
+        <v>6959377</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2834,7 +2834,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129744878</v>
+        <v>129745723</v>
       </c>
       <c r="B23" t="n">
         <v>57737</v>
@@ -2874,10 +2874,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>601263</v>
+        <v>601272</v>
       </c>
       <c r="R23" t="n">
-        <v>6959271</v>
+        <v>6959413</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2941,7 +2941,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129744814</v>
+        <v>129744878</v>
       </c>
       <c r="B24" t="n">
         <v>57737</v>
@@ -2981,10 +2981,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>601247</v>
+        <v>601263</v>
       </c>
       <c r="R24" t="n">
-        <v>6959312</v>
+        <v>6959271</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3048,7 +3048,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129745588</v>
+        <v>129744814</v>
       </c>
       <c r="B25" t="n">
         <v>57737</v>
@@ -3079,7 +3079,7 @@
       <c r="I25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3088,10 +3088,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>601286</v>
+        <v>601247</v>
       </c>
       <c r="R25" t="n">
-        <v>6959377</v>
+        <v>6959312</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>

--- a/artfynd/A 46081-2025 artfynd.xlsx
+++ b/artfynd/A 46081-2025 artfynd.xlsx
@@ -2004,7 +2004,7 @@
         <v>129743173</v>
       </c>
       <c r="B15" t="n">
-        <v>57578</v>
+        <v>57581</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2110,7 +2110,7 @@
         <v>129744699</v>
       </c>
       <c r="B16" t="n">
-        <v>57895</v>
+        <v>57898</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2216,7 +2216,7 @@
         <v>129743807</v>
       </c>
       <c r="B17" t="n">
-        <v>78842</v>
+        <v>78845</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2313,7 +2313,7 @@
         <v>129744479</v>
       </c>
       <c r="B18" t="n">
-        <v>57895</v>
+        <v>57898</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2415,7 +2415,7 @@
         <v>129744685</v>
       </c>
       <c r="B19" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2516,7 +2516,7 @@
         <v>129744133</v>
       </c>
       <c r="B20" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2623,7 +2623,7 @@
         <v>129745703</v>
       </c>
       <c r="B21" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2727,10 +2727,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129745588</v>
+        <v>129745723</v>
       </c>
       <c r="B22" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2758,7 +2758,7 @@
       <c r="I22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -2767,10 +2767,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>601286</v>
+        <v>601272</v>
       </c>
       <c r="R22" t="n">
-        <v>6959377</v>
+        <v>6959413</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2834,10 +2834,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129745723</v>
+        <v>129744878</v>
       </c>
       <c r="B23" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2874,10 +2874,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>601272</v>
+        <v>601263</v>
       </c>
       <c r="R23" t="n">
-        <v>6959413</v>
+        <v>6959271</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2941,10 +2941,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129744878</v>
+        <v>129744814</v>
       </c>
       <c r="B24" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2981,10 +2981,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>601263</v>
+        <v>601247</v>
       </c>
       <c r="R24" t="n">
-        <v>6959271</v>
+        <v>6959312</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3048,10 +3048,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129744814</v>
+        <v>129745588</v>
       </c>
       <c r="B25" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3079,7 +3079,7 @@
       <c r="I25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3088,10 +3088,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>601247</v>
+        <v>601286</v>
       </c>
       <c r="R25" t="n">
-        <v>6959312</v>
+        <v>6959377</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3158,7 +3158,7 @@
         <v>129744201</v>
       </c>
       <c r="B26" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3265,7 +3265,7 @@
         <v>129744421</v>
       </c>
       <c r="B27" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3372,7 +3372,7 @@
         <v>129745773</v>
       </c>
       <c r="B28" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3479,7 +3479,7 @@
         <v>129744312</v>
       </c>
       <c r="B29" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3586,7 +3586,7 @@
         <v>129742961</v>
       </c>
       <c r="B30" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3693,7 +3693,7 @@
         <v>129743133</v>
       </c>
       <c r="B31" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>

--- a/artfynd/A 46081-2025 artfynd.xlsx
+++ b/artfynd/A 46081-2025 artfynd.xlsx
@@ -2216,7 +2216,7 @@
         <v>129743807</v>
       </c>
       <c r="B17" t="n">
-        <v>78845</v>
+        <v>78846</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2415,7 +2415,7 @@
         <v>129744685</v>
       </c>
       <c r="B19" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2834,7 +2834,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129744878</v>
+        <v>129745588</v>
       </c>
       <c r="B23" t="n">
         <v>57740</v>
@@ -2865,7 +2865,7 @@
       <c r="I23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -2874,10 +2874,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>601263</v>
+        <v>601286</v>
       </c>
       <c r="R23" t="n">
-        <v>6959271</v>
+        <v>6959377</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3048,7 +3048,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129745588</v>
+        <v>129744878</v>
       </c>
       <c r="B25" t="n">
         <v>57740</v>
@@ -3079,7 +3079,7 @@
       <c r="I25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3088,10 +3088,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>601286</v>
+        <v>601263</v>
       </c>
       <c r="R25" t="n">
-        <v>6959377</v>
+        <v>6959271</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3262,7 +3262,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129744421</v>
+        <v>129745773</v>
       </c>
       <c r="B27" t="n">
         <v>57740</v>
@@ -3293,7 +3293,7 @@
       <c r="I27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -3302,10 +3302,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>601240</v>
+        <v>601280</v>
       </c>
       <c r="R27" t="n">
-        <v>6959385</v>
+        <v>6959438</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3369,7 +3369,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129745773</v>
+        <v>129744421</v>
       </c>
       <c r="B28" t="n">
         <v>57740</v>
@@ -3400,7 +3400,7 @@
       <c r="I28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -3409,10 +3409,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>601280</v>
+        <v>601240</v>
       </c>
       <c r="R28" t="n">
-        <v>6959438</v>
+        <v>6959385</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3449,7 +3449,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD28" t="b">

--- a/artfynd/A 46081-2025 artfynd.xlsx
+++ b/artfynd/A 46081-2025 artfynd.xlsx
@@ -2110,7 +2110,7 @@
         <v>129744699</v>
       </c>
       <c r="B16" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2216,7 +2216,7 @@
         <v>129743807</v>
       </c>
       <c r="B17" t="n">
-        <v>78846</v>
+        <v>78847</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2313,7 +2313,7 @@
         <v>129744479</v>
       </c>
       <c r="B18" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2415,7 +2415,7 @@
         <v>129744685</v>
       </c>
       <c r="B19" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 46081-2025 artfynd.xlsx
+++ b/artfynd/A 46081-2025 artfynd.xlsx
@@ -3799,7 +3799,7 @@
         <v>131106660</v>
       </c>
       <c r="B32" t="n">
-        <v>79002</v>
+        <v>79003</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3924,7 +3924,7 @@
         <v>131106663</v>
       </c>
       <c r="B33" t="n">
-        <v>79864</v>
+        <v>79865</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4054,7 +4054,7 @@
         <v>131106648</v>
       </c>
       <c r="B34" t="n">
-        <v>79864</v>
+        <v>79865</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4296,7 +4296,7 @@
         <v>131106661</v>
       </c>
       <c r="B36" t="n">
-        <v>79864</v>
+        <v>79865</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4423,32 +4423,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>131106643</v>
+        <v>131106649</v>
       </c>
       <c r="B37" t="n">
-        <v>78648</v>
+        <v>91825</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6437</v>
+        <v>1205</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -4458,7 +4458,7 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>cm²</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -4467,10 +4467,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>601129</v>
+        <v>601221</v>
       </c>
       <c r="R37" t="n">
-        <v>6959679</v>
+        <v>6959782</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4497,7 +4497,7 @@
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>2025_0533</t>
+          <t>2025_0527</t>
         </is>
       </c>
       <c r="Y37" t="inlineStr">
@@ -4507,7 +4507,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>09:07</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4517,7 +4517,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>09:07</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>aspstubbe</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4537,7 +4542,7 @@
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Samuel Koont</t>
+          <t>Måns Svensson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr">
@@ -4551,7 +4556,7 @@
         <v>131106646</v>
       </c>
       <c r="B38" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4669,32 +4674,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>131106649</v>
+        <v>131106643</v>
       </c>
       <c r="B39" t="n">
-        <v>91824</v>
+        <v>78649</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1205</v>
+        <v>6437</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -4704,7 +4709,7 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>cm²</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
@@ -4713,10 +4718,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>601221</v>
+        <v>601129</v>
       </c>
       <c r="R39" t="n">
-        <v>6959782</v>
+        <v>6959679</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4743,7 +4748,7 @@
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>2025_0527</t>
+          <t>2025_0533</t>
         </is>
       </c>
       <c r="Y39" t="inlineStr">
@@ -4753,7 +4758,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>09:07</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4763,12 +4768,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>09:07</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>aspstubbe</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4788,7 +4788,7 @@
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Måns Svensson</t>
+          <t>Samuel Koont</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr">
@@ -4802,7 +4802,7 @@
         <v>131106645</v>
       </c>
       <c r="B40" t="n">
-        <v>98935</v>
+        <v>98936</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/artfynd/A 46081-2025 artfynd.xlsx
+++ b/artfynd/A 46081-2025 artfynd.xlsx
@@ -3799,7 +3799,7 @@
         <v>131106660</v>
       </c>
       <c r="B32" t="n">
-        <v>79003</v>
+        <v>79005</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3924,7 +3924,7 @@
         <v>131106663</v>
       </c>
       <c r="B33" t="n">
-        <v>79865</v>
+        <v>79867</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4051,10 +4051,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131106648</v>
+        <v>131106659</v>
       </c>
       <c r="B34" t="n">
-        <v>79865</v>
+        <v>57886</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4062,21 +4062,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4086,10 +4086,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>601198</v>
+        <v>601218</v>
       </c>
       <c r="R34" t="n">
-        <v>6959731</v>
+        <v>6959810</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4116,7 +4116,7 @@
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>2025_0528</t>
+          <t>2025_0517</t>
         </is>
       </c>
       <c r="Y34" t="inlineStr">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>08:33</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4136,12 +4136,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>08:33</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Brandpåverkad tallstubbe</t>
+          <t>På gran i barrblandskog. Ev. liten hackspett, men är med stor sannolikhet tretåig hackspett enligt diskussion med Anders Forsberg.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4172,10 +4172,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131106659</v>
+        <v>131106648</v>
       </c>
       <c r="B35" t="n">
-        <v>57884</v>
+        <v>79867</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4183,21 +4183,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4207,10 +4207,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>601218</v>
+        <v>601198</v>
       </c>
       <c r="R35" t="n">
-        <v>6959810</v>
+        <v>6959731</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4237,7 +4237,7 @@
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>2025_0517</t>
+          <t>2025_0528</t>
         </is>
       </c>
       <c r="Y35" t="inlineStr">
@@ -4247,7 +4247,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>08:33</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4257,12 +4257,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>08:33</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>På gran i barrblandskog. Ev. liten hackspett, men är med stor sannolikhet tretåig hackspett enligt diskussion med Anders Forsberg.</t>
+          <t>Brandpåverkad tallstubbe</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4296,7 +4296,7 @@
         <v>131106661</v>
       </c>
       <c r="B36" t="n">
-        <v>79865</v>
+        <v>79867</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4426,7 +4426,7 @@
         <v>131106649</v>
       </c>
       <c r="B37" t="n">
-        <v>91825</v>
+        <v>91827</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4556,7 +4556,7 @@
         <v>131106646</v>
       </c>
       <c r="B38" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4677,7 +4677,7 @@
         <v>131106643</v>
       </c>
       <c r="B39" t="n">
-        <v>78649</v>
+        <v>78651</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4802,7 +4802,7 @@
         <v>131106645</v>
       </c>
       <c r="B40" t="n">
-        <v>98936</v>
+        <v>98938</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/artfynd/A 46081-2025 artfynd.xlsx
+++ b/artfynd/A 46081-2025 artfynd.xlsx
@@ -3799,7 +3799,7 @@
         <v>131106660</v>
       </c>
       <c r="B32" t="n">
-        <v>79005</v>
+        <v>79006</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3924,7 +3924,7 @@
         <v>131106663</v>
       </c>
       <c r="B33" t="n">
-        <v>79867</v>
+        <v>79868</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4054,7 +4054,7 @@
         <v>131106659</v>
       </c>
       <c r="B34" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4175,7 +4175,7 @@
         <v>131106648</v>
       </c>
       <c r="B35" t="n">
-        <v>79867</v>
+        <v>79868</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4296,7 +4296,7 @@
         <v>131106661</v>
       </c>
       <c r="B36" t="n">
-        <v>79867</v>
+        <v>79868</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4426,7 +4426,7 @@
         <v>131106649</v>
       </c>
       <c r="B37" t="n">
-        <v>91827</v>
+        <v>91828</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4556,7 +4556,7 @@
         <v>131106646</v>
       </c>
       <c r="B38" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4677,7 +4677,7 @@
         <v>131106643</v>
       </c>
       <c r="B39" t="n">
-        <v>78651</v>
+        <v>78652</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4802,7 +4802,7 @@
         <v>131106645</v>
       </c>
       <c r="B40" t="n">
-        <v>98938</v>
+        <v>98939</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/artfynd/A 46081-2025 artfynd.xlsx
+++ b/artfynd/A 46081-2025 artfynd.xlsx
@@ -4051,10 +4051,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131106659</v>
+        <v>131106648</v>
       </c>
       <c r="B34" t="n">
-        <v>57887</v>
+        <v>79868</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4062,21 +4062,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4086,10 +4086,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>601218</v>
+        <v>601198</v>
       </c>
       <c r="R34" t="n">
-        <v>6959810</v>
+        <v>6959731</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4116,7 +4116,7 @@
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>2025_0517</t>
+          <t>2025_0528</t>
         </is>
       </c>
       <c r="Y34" t="inlineStr">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>08:33</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4136,12 +4136,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>08:33</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>På gran i barrblandskog. Ev. liten hackspett, men är med stor sannolikhet tretåig hackspett enligt diskussion med Anders Forsberg.</t>
+          <t>Brandpåverkad tallstubbe</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4172,10 +4172,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131106648</v>
+        <v>131106659</v>
       </c>
       <c r="B35" t="n">
-        <v>79868</v>
+        <v>57887</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4183,21 +4183,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4207,10 +4207,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>601198</v>
+        <v>601218</v>
       </c>
       <c r="R35" t="n">
-        <v>6959731</v>
+        <v>6959810</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4237,7 +4237,7 @@
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>2025_0528</t>
+          <t>2025_0517</t>
         </is>
       </c>
       <c r="Y35" t="inlineStr">
@@ -4247,7 +4247,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>08:33</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4257,12 +4257,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>08:33</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Brandpåverkad tallstubbe</t>
+          <t>På gran i barrblandskog. Ev. liten hackspett, men är med stor sannolikhet tretåig hackspett enligt diskussion med Anders Forsberg.</t>
         </is>
       </c>
       <c r="AD35" t="b">

--- a/artfynd/A 46081-2025 artfynd.xlsx
+++ b/artfynd/A 46081-2025 artfynd.xlsx
@@ -3799,7 +3799,7 @@
         <v>131106660</v>
       </c>
       <c r="B32" t="n">
-        <v>79006</v>
+        <v>79007</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3924,7 +3924,7 @@
         <v>131106663</v>
       </c>
       <c r="B33" t="n">
-        <v>79868</v>
+        <v>79869</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4054,7 +4054,7 @@
         <v>131106648</v>
       </c>
       <c r="B34" t="n">
-        <v>79868</v>
+        <v>79869</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4175,7 +4175,7 @@
         <v>131106659</v>
       </c>
       <c r="B35" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4296,7 +4296,7 @@
         <v>131106661</v>
       </c>
       <c r="B36" t="n">
-        <v>79868</v>
+        <v>79869</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4426,7 +4426,7 @@
         <v>131106649</v>
       </c>
       <c r="B37" t="n">
-        <v>91828</v>
+        <v>91829</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4556,7 +4556,7 @@
         <v>131106646</v>
       </c>
       <c r="B38" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4677,7 +4677,7 @@
         <v>131106643</v>
       </c>
       <c r="B39" t="n">
-        <v>78652</v>
+        <v>78653</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4802,7 +4802,7 @@
         <v>131106645</v>
       </c>
       <c r="B40" t="n">
-        <v>98939</v>
+        <v>98940</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/artfynd/A 46081-2025 artfynd.xlsx
+++ b/artfynd/A 46081-2025 artfynd.xlsx
@@ -4423,54 +4423,45 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>131106649</v>
+        <v>131106646</v>
       </c>
       <c r="B37" t="n">
-        <v>91829</v>
+        <v>79250</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1205</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Niemelä</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Lappberget, Mpd</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>601221</v>
+        <v>601173</v>
       </c>
       <c r="R37" t="n">
-        <v>6959782</v>
+        <v>6959739</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4497,7 +4488,7 @@
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>2025_0527</t>
+          <t>2025_0530</t>
         </is>
       </c>
       <c r="Y37" t="inlineStr">
@@ -4507,7 +4498,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>09:07</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4517,12 +4508,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>09:07</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>aspstubbe</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4553,10 +4544,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>131106646</v>
+        <v>131106643</v>
       </c>
       <c r="B38" t="n">
-        <v>79250</v>
+        <v>78653</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4564,34 +4555,43 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>6437</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>cm²</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Lappberget, Mpd</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>601173</v>
+        <v>601129</v>
       </c>
       <c r="R38" t="n">
-        <v>6959739</v>
+        <v>6959679</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4618,7 +4618,7 @@
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>2025_0530</t>
+          <t>2025_0533</t>
         </is>
       </c>
       <c r="Y38" t="inlineStr">
@@ -4628,7 +4628,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>09:36</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4638,12 +4638,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>09:36</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>tall</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4663,7 +4658,7 @@
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Måns Svensson</t>
+          <t>Samuel Koont</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr">
@@ -4674,32 +4669,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>131106643</v>
+        <v>131106649</v>
       </c>
       <c r="B39" t="n">
-        <v>78653</v>
+        <v>91829</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6437</v>
+        <v>1205</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -4709,7 +4704,7 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>cm²</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
@@ -4718,10 +4713,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>601129</v>
+        <v>601221</v>
       </c>
       <c r="R39" t="n">
-        <v>6959679</v>
+        <v>6959782</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4748,7 +4743,7 @@
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>2025_0533</t>
+          <t>2025_0527</t>
         </is>
       </c>
       <c r="Y39" t="inlineStr">
@@ -4758,7 +4753,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>09:07</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4768,7 +4763,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>09:07</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>aspstubbe</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4788,7 +4788,7 @@
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Samuel Koont</t>
+          <t>Måns Svensson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr">

--- a/artfynd/A 46081-2025 artfynd.xlsx
+++ b/artfynd/A 46081-2025 artfynd.xlsx
@@ -3799,7 +3799,7 @@
         <v>131106660</v>
       </c>
       <c r="B32" t="n">
-        <v>79007</v>
+        <v>79010</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3924,7 +3924,7 @@
         <v>131106663</v>
       </c>
       <c r="B33" t="n">
-        <v>79869</v>
+        <v>79872</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4054,7 +4054,7 @@
         <v>131106648</v>
       </c>
       <c r="B34" t="n">
-        <v>79869</v>
+        <v>79872</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4175,7 +4175,7 @@
         <v>131106659</v>
       </c>
       <c r="B35" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4296,7 +4296,7 @@
         <v>131106661</v>
       </c>
       <c r="B36" t="n">
-        <v>79869</v>
+        <v>79872</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4426,7 +4426,7 @@
         <v>131106646</v>
       </c>
       <c r="B37" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4547,7 +4547,7 @@
         <v>131106643</v>
       </c>
       <c r="B38" t="n">
-        <v>78653</v>
+        <v>78656</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4672,7 +4672,7 @@
         <v>131106649</v>
       </c>
       <c r="B39" t="n">
-        <v>91829</v>
+        <v>91832</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4802,7 +4802,7 @@
         <v>131106645</v>
       </c>
       <c r="B40" t="n">
-        <v>98940</v>
+        <v>98943</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/artfynd/A 46081-2025 artfynd.xlsx
+++ b/artfynd/A 46081-2025 artfynd.xlsx
@@ -3799,7 +3799,7 @@
         <v>131106660</v>
       </c>
       <c r="B32" t="n">
-        <v>79010</v>
+        <v>79011</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3924,7 +3924,7 @@
         <v>131106663</v>
       </c>
       <c r="B33" t="n">
-        <v>79872</v>
+        <v>79873</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4054,7 +4054,7 @@
         <v>131106648</v>
       </c>
       <c r="B34" t="n">
-        <v>79872</v>
+        <v>79873</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4175,7 +4175,7 @@
         <v>131106659</v>
       </c>
       <c r="B35" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4296,7 +4296,7 @@
         <v>131106661</v>
       </c>
       <c r="B36" t="n">
-        <v>79872</v>
+        <v>79873</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4423,45 +4423,54 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>131106646</v>
+        <v>131106649</v>
       </c>
       <c r="B37" t="n">
-        <v>79253</v>
+        <v>91833</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>1205</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Lappberget, Mpd</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>601173</v>
+        <v>601221</v>
       </c>
       <c r="R37" t="n">
-        <v>6959739</v>
+        <v>6959782</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4488,7 +4497,7 @@
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>2025_0530</t>
+          <t>2025_0527</t>
         </is>
       </c>
       <c r="Y37" t="inlineStr">
@@ -4498,7 +4507,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>09:36</t>
+          <t>09:07</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4508,12 +4517,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>09:36</t>
+          <t>09:07</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>aspstubbe</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4544,10 +4553,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>131106643</v>
+        <v>131106646</v>
       </c>
       <c r="B38" t="n">
-        <v>78656</v>
+        <v>79254</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4555,43 +4564,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6437</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>cm²</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Lappberget, Mpd</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>601129</v>
+        <v>601173</v>
       </c>
       <c r="R38" t="n">
-        <v>6959679</v>
+        <v>6959739</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4618,7 +4618,7 @@
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>2025_0533</t>
+          <t>2025_0530</t>
         </is>
       </c>
       <c r="Y38" t="inlineStr">
@@ -4628,7 +4628,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4638,7 +4638,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>09:36</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>tall</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4658,7 +4663,7 @@
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Samuel Koont</t>
+          <t>Måns Svensson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr">
@@ -4669,32 +4674,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>131106649</v>
+        <v>131106643</v>
       </c>
       <c r="B39" t="n">
-        <v>91832</v>
+        <v>78657</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1205</v>
+        <v>6437</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -4704,7 +4709,7 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>cm²</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
@@ -4713,10 +4718,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>601221</v>
+        <v>601129</v>
       </c>
       <c r="R39" t="n">
-        <v>6959782</v>
+        <v>6959679</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4743,7 +4748,7 @@
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>2025_0527</t>
+          <t>2025_0533</t>
         </is>
       </c>
       <c r="Y39" t="inlineStr">
@@ -4753,7 +4758,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>09:07</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4763,12 +4768,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>09:07</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>aspstubbe</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4788,7 +4788,7 @@
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Måns Svensson</t>
+          <t>Samuel Koont</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr">
@@ -4802,7 +4802,7 @@
         <v>131106645</v>
       </c>
       <c r="B40" t="n">
-        <v>98943</v>
+        <v>98944</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/artfynd/A 46081-2025 artfynd.xlsx
+++ b/artfynd/A 46081-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY40"/>
+  <dimension ref="A1:AY56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>112538838</v>
+        <v>112538840</v>
       </c>
       <c r="B2" t="n">
-        <v>90945</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5966</v>
+        <v>353</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>601357</v>
+        <v>601305</v>
       </c>
       <c r="R2" t="n">
-        <v>6959588</v>
+        <v>6959617</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,50 +772,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>112538832</v>
+        <v>129742520</v>
       </c>
       <c r="B3" t="n">
-        <v>90965</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80305</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5448</v>
+        <v>392</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Aspgelélav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Collema subnigrescens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
+          <t>Degel.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Stor-skälsjön, Mpd</t>
+          <t>Lappberget, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>601307</v>
+        <v>601280</v>
       </c>
       <c r="R3" t="n">
-        <v>6959564</v>
+        <v>6959783</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -847,12 +837,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-09-30</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-09-30</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -867,27 +857,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Rasmus Viding</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Rasmus Viding</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>112538834</v>
+        <v>131106656</v>
       </c>
       <c r="B4" t="n">
-        <v>96886</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80305</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -895,34 +880,43 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>392</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Aspgelélav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Collema subnigrescens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>Degel.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Stor-skälsjön, Mpd</t>
+          <t>Lappberget, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>601229</v>
+        <v>601270</v>
       </c>
       <c r="R4" t="n">
-        <v>6959270</v>
+        <v>6959748</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -947,14 +941,34 @@
           <t>Ljustorp</t>
         </is>
       </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>2025_0520</t>
+        </is>
+      </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2023-09-30</t>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>08:43</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2023-09-30</t>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>08:43</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>asphögstubbe</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -969,62 +983,70 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Rasmus Viding</t>
+          <t>David Isaksson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Rasmus Viding</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr"/>
+          <t>Måns Svensson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Kustpaketet</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>112538843</v>
+        <v>131106658</v>
       </c>
       <c r="B5" t="n">
-        <v>88745</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80305</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1962</v>
+        <v>392</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Aspgelélav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Collema subnigrescens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>Degel.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Stor-skälsjön, Mpd</t>
+          <t>Lappberget, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>601234</v>
+        <v>601282</v>
       </c>
       <c r="R5" t="n">
-        <v>6959631</v>
+        <v>6959785</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1049,14 +1071,29 @@
           <t>Ljustorp</t>
         </is>
       </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>2025_0518</t>
+        </is>
+      </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2023-09-30</t>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>08:35</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2023-09-30</t>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>08:35</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1071,27 +1108,26 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Rasmus Viding</t>
+          <t>David Isaksson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Rasmus Viding</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr"/>
+          <t>Samuel Koont</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Kustpaketet</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>112538840</v>
+        <v>112538841</v>
       </c>
       <c r="B6" t="n">
-        <v>77417</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>81312</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1099,21 +1135,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>353</v>
+        <v>1049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1159,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>601305</v>
+        <v>601234</v>
       </c>
       <c r="R6" t="n">
-        <v>6959617</v>
+        <v>6959631</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,15 +1221,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>112538842</v>
+        <v>112538853</v>
       </c>
       <c r="B7" t="n">
-        <v>78338</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>81312</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1201,21 +1232,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6453</v>
+        <v>1049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1256,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>601234</v>
+        <v>601142</v>
       </c>
       <c r="R7" t="n">
-        <v>6959631</v>
+        <v>6959195</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1255,12 +1286,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2023-09-30</t>
+          <t>2023-09-29</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2023-09-30</t>
+          <t>2023-09-29</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1287,15 +1318,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>112538839</v>
+        <v>131106649</v>
       </c>
       <c r="B8" t="n">
-        <v>90922</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91920</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1303,34 +1329,43 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4364</v>
+        <v>1205</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Stor-skälsjön, Mpd</t>
+          <t>Lappberget, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>601305</v>
+        <v>601221</v>
       </c>
       <c r="R8" t="n">
-        <v>6959617</v>
+        <v>6959782</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1355,14 +1390,34 @@
           <t>Ljustorp</t>
         </is>
       </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>2025_0527</t>
+        </is>
+      </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2023-09-30</t>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>09:07</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2023-09-30</t>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>09:07</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>aspstubbe</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1377,27 +1432,26 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Rasmus Viding</t>
+          <t>David Isaksson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Rasmus Viding</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr"/>
+          <t>Måns Svensson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Kustpaketet</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>112538847</v>
+        <v>112538843</v>
       </c>
       <c r="B9" t="n">
-        <v>77746</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90932</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1405,21 +1459,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>1962</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1483,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>601208</v>
+        <v>601234</v>
       </c>
       <c r="R9" t="n">
-        <v>6959777</v>
+        <v>6959631</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1491,37 +1545,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>112538836</v>
+        <v>112538837</v>
       </c>
       <c r="B10" t="n">
-        <v>78743</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6456</v>
+        <v>4362</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1531,10 +1580,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>601284</v>
+        <v>601389</v>
       </c>
       <c r="R10" t="n">
-        <v>6959331</v>
+        <v>6959445</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1593,15 +1642,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>112538837</v>
+        <v>112538839</v>
       </c>
       <c r="B11" t="n">
-        <v>90916</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1609,21 +1653,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1633,10 +1677,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>601389</v>
+        <v>601305</v>
       </c>
       <c r="R11" t="n">
-        <v>6959445</v>
+        <v>6959617</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1695,50 +1739,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>112538846</v>
+        <v>129742766</v>
       </c>
       <c r="B12" t="n">
-        <v>77498</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91893</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6446</v>
+        <v>4660</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Rävticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Inocutis rheades</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Stor-skälsjön, Mpd</t>
+          <t>Lappberget, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>601223</v>
+        <v>601279</v>
       </c>
       <c r="R12" t="n">
-        <v>6959727</v>
+        <v>6959688</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1765,12 +1804,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2023-09-30</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2023-09-30</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1785,49 +1824,44 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Rasmus Viding</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Rasmus Viding</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>112538844</v>
+        <v>112538832</v>
       </c>
       <c r="B13" t="n">
-        <v>96886</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93223</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>5448</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Sw. ex Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1837,10 +1871,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>601219</v>
+        <v>601307</v>
       </c>
       <c r="R13" t="n">
-        <v>6959653</v>
+        <v>6959564</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1899,15 +1933,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>112538841</v>
+        <v>112538838</v>
       </c>
       <c r="B14" t="n">
-        <v>79676</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1915,21 +1944,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1049</v>
+        <v>5966</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1939,10 +1968,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>601234</v>
+        <v>601357</v>
       </c>
       <c r="R14" t="n">
-        <v>6959631</v>
+        <v>6959588</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2001,54 +2030,45 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129743173</v>
+        <v>112538847</v>
       </c>
       <c r="B15" t="n">
-        <v>57581</v>
+        <v>79327</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>102621</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Lappberget, Mpd</t>
+          <t>Stor-skälsjön, Mpd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>601219</v>
+        <v>601208</v>
       </c>
       <c r="R15" t="n">
-        <v>6959648</v>
+        <v>6959777</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2075,12 +2095,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2023-09-30</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2023-09-30</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2095,66 +2115,57 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Rasmus Viding</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Rasmus Viding</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129744699</v>
+        <v>131106646</v>
       </c>
       <c r="B16" t="n">
-        <v>57899</v>
+        <v>79327</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Alderbackberget, Mpd</t>
+          <t>Lappberget, Mpd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>601189</v>
+        <v>601173</v>
       </c>
       <c r="R16" t="n">
-        <v>6959263</v>
+        <v>6959739</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2179,14 +2190,34 @@
           <t>Ljustorp</t>
         </is>
       </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>2025_0530</t>
+        </is>
+      </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>09:36</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>tall</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2201,22 +2232,26 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>David Isaksson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
-        </is>
-      </c>
-      <c r="AY16" t="inlineStr"/>
+          <t>Måns Svensson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>Kustpaketet</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129743807</v>
+        <v>131106643</v>
       </c>
       <c r="B17" t="n">
-        <v>78852</v>
+        <v>78730</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2224,34 +2259,43 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>228912</v>
+        <v>6437</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>cm²</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Lappberget, Mpd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>601219</v>
+        <v>601129</v>
       </c>
       <c r="R17" t="n">
-        <v>6959554</v>
+        <v>6959679</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2276,14 +2320,29 @@
           <t>Ljustorp</t>
         </is>
       </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>2025_0533</t>
+        </is>
+      </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2298,22 +2357,26 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>David Isaksson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
-        </is>
-      </c>
-      <c r="AY17" t="inlineStr"/>
+          <t>Samuel Koont</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>Kustpaketet</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129744479</v>
+        <v>112538846</v>
       </c>
       <c r="B18" t="n">
-        <v>57899</v>
+        <v>79084</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2321,39 +2384,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103021</v>
+        <v>6446</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Alderbackberget, Mpd</t>
+          <t>Stor-skälsjön, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>601226</v>
+        <v>601223</v>
       </c>
       <c r="R18" t="n">
-        <v>6959363</v>
+        <v>6959727</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2380,12 +2438,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2023-09-30</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2023-09-30</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2400,61 +2458,57 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Rasmus Viding</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Rasmus Viding</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129744685</v>
+        <v>112538854</v>
       </c>
       <c r="B19" t="n">
-        <v>98830</v>
+        <v>79084</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Alderbackberget, Mpd</t>
+          <t>Stor-skälsjön, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>601189</v>
+        <v>601142</v>
       </c>
       <c r="R19" t="n">
-        <v>6959263</v>
+        <v>6959195</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2481,12 +2535,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2023-09-29</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2023-09-29</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2501,22 +2555,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Rasmus Viding</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Rasmus Viding</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129744133</v>
+        <v>129742454</v>
       </c>
       <c r="B20" t="n">
-        <v>57741</v>
+        <v>79084</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2524,39 +2578,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Lappberget, Mpd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>601222</v>
+        <v>601273</v>
       </c>
       <c r="R20" t="n">
-        <v>6959449</v>
+        <v>6959833</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2589,11 +2638,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-11-18</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2620,10 +2664,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129745703</v>
+        <v>131106660</v>
       </c>
       <c r="B21" t="n">
-        <v>57741</v>
+        <v>79084</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2631,39 +2675,43 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>dm²</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Alderbackberget, Mpd</t>
+          <t>Lappberget, Mpd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>601258</v>
+        <v>601244</v>
       </c>
       <c r="R21" t="n">
-        <v>6959417</v>
+        <v>6959831</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2688,19 +2736,29 @@
           <t>Ljustorp</t>
         </is>
       </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>2025_0516</t>
+        </is>
+      </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>08:28</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>08:28</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2715,22 +2773,26 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>David Isaksson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
-        </is>
-      </c>
-      <c r="AY21" t="inlineStr"/>
+          <t>Samuel Koont</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr">
+        <is>
+          <t>Kustpaketet</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129745723</v>
+        <v>112538842</v>
       </c>
       <c r="B22" t="n">
-        <v>57741</v>
+        <v>79946</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2738,39 +2800,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Alderbackberget, Mpd</t>
+          <t>Stor-skälsjön, Mpd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>601272</v>
+        <v>601234</v>
       </c>
       <c r="R22" t="n">
-        <v>6959413</v>
+        <v>6959631</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2797,17 +2854,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2023-09-30</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>2023-09-30</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2822,22 +2874,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Rasmus Viding</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Rasmus Viding</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129744878</v>
+        <v>112538856</v>
       </c>
       <c r="B23" t="n">
-        <v>57741</v>
+        <v>79946</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2845,39 +2897,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Alderbackberget, Mpd</t>
+          <t>Stor-skälsjön, Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>601263</v>
+        <v>601142</v>
       </c>
       <c r="R23" t="n">
-        <v>6959271</v>
+        <v>6959195</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2904,17 +2951,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2023-09-29</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>2023-09-29</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2929,22 +2971,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Rasmus Viding</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Rasmus Viding</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129744814</v>
+        <v>131106648</v>
       </c>
       <c r="B24" t="n">
-        <v>57741</v>
+        <v>79946</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2952,39 +2994,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Alderbackberget, Mpd</t>
+          <t>Lappberget, Mpd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>601247</v>
+        <v>601198</v>
       </c>
       <c r="R24" t="n">
-        <v>6959312</v>
+        <v>6959731</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3009,19 +3046,34 @@
           <t>Ljustorp</t>
         </is>
       </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>2025_0528</t>
+        </is>
+      </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Brandpåverkad tallstubbe</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3036,22 +3088,26 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>David Isaksson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
-        </is>
-      </c>
-      <c r="AY24" t="inlineStr"/>
+          <t>Karin Halldin</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr">
+        <is>
+          <t>Kustpaketet</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129745588</v>
+        <v>131106661</v>
       </c>
       <c r="B25" t="n">
-        <v>57741</v>
+        <v>79946</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3059,39 +3115,43 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>dm²</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Alderbackberget, Mpd</t>
+          <t>Lappberget, Mpd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>601286</v>
+        <v>601240</v>
       </c>
       <c r="R25" t="n">
-        <v>6959377</v>
+        <v>6959782</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3116,19 +3176,34 @@
           <t>Ljustorp</t>
         </is>
       </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>2025_0515</t>
+        </is>
+      </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>08:26</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>08:26</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>tallstubbe</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3143,22 +3218,26 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>David Isaksson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
-        </is>
-      </c>
-      <c r="AY25" t="inlineStr"/>
+          <t>Måns Svensson</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr">
+        <is>
+          <t>Kustpaketet</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129744201</v>
+        <v>131106663</v>
       </c>
       <c r="B26" t="n">
-        <v>57741</v>
+        <v>79946</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3166,27 +3245,31 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>dm²</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3195,10 +3278,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>601224</v>
+        <v>601228</v>
       </c>
       <c r="R26" t="n">
-        <v>6959429</v>
+        <v>6959812</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3223,19 +3306,34 @@
           <t>Ljustorp</t>
         </is>
       </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>2025_0513</t>
+        </is>
+      </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>08:22</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>08:22</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>tallstubbe</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3250,62 +3348,61 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>David Isaksson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
-        </is>
-      </c>
-      <c r="AY26" t="inlineStr"/>
+          <t>Måns Svensson</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr">
+        <is>
+          <t>Kustpaketet</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129745773</v>
+        <v>112538836</v>
       </c>
       <c r="B27" t="n">
-        <v>57741</v>
+        <v>80336</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>6456</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Alderbackberget, Mpd</t>
+          <t>Stor-skälsjön, Mpd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>601280</v>
+        <v>601284</v>
       </c>
       <c r="R27" t="n">
-        <v>6959438</v>
+        <v>6959331</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3332,17 +3429,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2023-09-30</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>2023-09-30</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3357,62 +3449,57 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Rasmus Viding</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Rasmus Viding</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129744421</v>
+        <v>129742486</v>
       </c>
       <c r="B28" t="n">
-        <v>57741</v>
+        <v>80336</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>6456</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Alderbackberget, Mpd</t>
+          <t>Lappberget, Mpd</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>601240</v>
+        <v>601273</v>
       </c>
       <c r="R28" t="n">
-        <v>6959385</v>
+        <v>6959833</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3445,11 +3532,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-11-18</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3476,10 +3558,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129744312</v>
+        <v>131106655</v>
       </c>
       <c r="B29" t="n">
-        <v>57741</v>
+        <v>80432</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3487,39 +3569,43 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Alderbackberget, Mpd</t>
+          <t>Lappberget, Mpd</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>601225</v>
+        <v>601279</v>
       </c>
       <c r="R29" t="n">
-        <v>6959403</v>
+        <v>6959779</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3544,19 +3630,29 @@
           <t>Ljustorp</t>
         </is>
       </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>2025_0521</t>
+        </is>
+      </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>08:44</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>08:44</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3571,22 +3667,26 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>David Isaksson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
-        </is>
-      </c>
-      <c r="AY29" t="inlineStr"/>
+          <t>Samuel Koont</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr">
+        <is>
+          <t>Kustpaketet</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129742961</v>
+        <v>131106657</v>
       </c>
       <c r="B30" t="n">
-        <v>57741</v>
+        <v>80432</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3594,27 +3694,31 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -3623,10 +3727,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>601187</v>
+        <v>601264</v>
       </c>
       <c r="R30" t="n">
-        <v>6959691</v>
+        <v>6959676</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3651,19 +3755,34 @@
           <t>Ljustorp</t>
         </is>
       </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>2025_0519</t>
+        </is>
+      </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>08:36</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>08:36</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>gammal asp</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3678,22 +3797,26 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>David Isaksson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
-        </is>
-      </c>
-      <c r="AY30" t="inlineStr"/>
+          <t>Måns Svensson</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr">
+        <is>
+          <t>Kustpaketet</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129743133</v>
+        <v>131106644</v>
       </c>
       <c r="B31" t="n">
-        <v>57741</v>
+        <v>78334</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3701,21 +3824,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>6487</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -3723,9 +3846,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>födosökande</t>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -3734,10 +3857,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>601237</v>
+        <v>601127</v>
       </c>
       <c r="R31" t="n">
-        <v>6959656</v>
+        <v>6959675</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3762,14 +3885,29 @@
           <t>Ljustorp</t>
         </is>
       </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>2025_0532</t>
+        </is>
+      </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3784,44 +3922,48 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>David Isaksson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
-        </is>
-      </c>
-      <c r="AY31" t="inlineStr"/>
+          <t>Samuel Koont</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr">
+        <is>
+          <t>Kustpaketet</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131106660</v>
+        <v>131106662</v>
       </c>
       <c r="B32" t="n">
-        <v>79011</v>
+        <v>57950</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -3829,21 +3971,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Lappberget, Mpd</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>601244</v>
+        <v>601246</v>
       </c>
       <c r="R32" t="n">
-        <v>6959831</v>
+        <v>6959852</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3870,7 +4007,7 @@
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>2025_0516</t>
+          <t>2025_0514</t>
         </is>
       </c>
       <c r="Y32" t="inlineStr">
@@ -3880,7 +4017,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>08:28</t>
+          <t>08:25</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3890,7 +4027,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>08:28</t>
+          <t>08:25</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Hackspår av spillkråka</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3921,10 +4063,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131106663</v>
+        <v>129742961</v>
       </c>
       <c r="B33" t="n">
-        <v>79873</v>
+        <v>57953</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3932,31 +4074,27 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>dm²</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -3965,10 +4103,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>601228</v>
+        <v>601187</v>
       </c>
       <c r="R33" t="n">
-        <v>6959812</v>
+        <v>6959691</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3993,34 +4131,19 @@
           <t>Ljustorp</t>
         </is>
       </c>
-      <c r="X33" t="inlineStr">
-        <is>
-          <t>2025_0513</t>
-        </is>
-      </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
-        </is>
-      </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>08:22</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>08:22</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>tallstubbe</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4035,26 +4158,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>David Isaksson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Måns Svensson</t>
-        </is>
-      </c>
-      <c r="AY33" t="inlineStr">
-        <is>
-          <t>Kustpaketet</t>
-        </is>
-      </c>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131106648</v>
+        <v>129743133</v>
       </c>
       <c r="B34" t="n">
-        <v>79873</v>
+        <v>57953</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4062,34 +4181,43 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Lappberget, Mpd</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>601198</v>
+        <v>601237</v>
       </c>
       <c r="R34" t="n">
-        <v>6959731</v>
+        <v>6959656</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4114,34 +4242,14 @@
           <t>Ljustorp</t>
         </is>
       </c>
-      <c r="X34" t="inlineStr">
-        <is>
-          <t>2025_0528</t>
-        </is>
-      </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
-        </is>
-      </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>09:15</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>09:15</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Brandpåverkad tallstubbe</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4156,26 +4264,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>David Isaksson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Karin Halldin</t>
-        </is>
-      </c>
-      <c r="AY34" t="inlineStr">
-        <is>
-          <t>Kustpaketet</t>
-        </is>
-      </c>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131106659</v>
+        <v>129744133</v>
       </c>
       <c r="B35" t="n">
-        <v>57892</v>
+        <v>57953</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4201,16 +4305,21 @@
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Lappberget, Mpd</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>601218</v>
+        <v>601222</v>
       </c>
       <c r="R35" t="n">
-        <v>6959810</v>
+        <v>6959449</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4235,34 +4344,19 @@
           <t>Ljustorp</t>
         </is>
       </c>
-      <c r="X35" t="inlineStr">
-        <is>
-          <t>2025_0517</t>
-        </is>
-      </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
-        </is>
-      </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>08:33</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>08:33</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>På gran i barrblandskog. Ev. liten hackspett, men är med stor sannolikhet tretåig hackspett enligt diskussion med Anders Forsberg.</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4277,26 +4371,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>David Isaksson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Karin Halldin</t>
-        </is>
-      </c>
-      <c r="AY35" t="inlineStr">
-        <is>
-          <t>Kustpaketet</t>
-        </is>
-      </c>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>131106661</v>
+        <v>129744201</v>
       </c>
       <c r="B36" t="n">
-        <v>79873</v>
+        <v>57953</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4304,31 +4394,27 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>dm²</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -4337,10 +4423,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>601240</v>
+        <v>601224</v>
       </c>
       <c r="R36" t="n">
-        <v>6959782</v>
+        <v>6959429</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4365,34 +4451,19 @@
           <t>Ljustorp</t>
         </is>
       </c>
-      <c r="X36" t="inlineStr">
-        <is>
-          <t>2025_0515</t>
-        </is>
-      </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
-        </is>
-      </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>08:26</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>08:26</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>tallstubbe</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4407,70 +4478,62 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>David Isaksson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Måns Svensson</t>
-        </is>
-      </c>
-      <c r="AY36" t="inlineStr">
-        <is>
-          <t>Kustpaketet</t>
-        </is>
-      </c>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>131106649</v>
+        <v>129744312</v>
       </c>
       <c r="B37" t="n">
-        <v>91833</v>
+        <v>57953</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1205</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Niemelä</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>mycel</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Lappberget, Mpd</t>
+          <t>Alderbackberget, Mpd</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>601221</v>
+        <v>601225</v>
       </c>
       <c r="R37" t="n">
-        <v>6959782</v>
+        <v>6959403</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4495,34 +4558,19 @@
           <t>Ljustorp</t>
         </is>
       </c>
-      <c r="X37" t="inlineStr">
-        <is>
-          <t>2025_0527</t>
-        </is>
-      </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
-        </is>
-      </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>09:07</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>09:07</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>aspstubbe</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4537,26 +4585,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>David Isaksson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Måns Svensson</t>
-        </is>
-      </c>
-      <c r="AY37" t="inlineStr">
-        <is>
-          <t>Kustpaketet</t>
-        </is>
-      </c>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>131106646</v>
+        <v>129744421</v>
       </c>
       <c r="B38" t="n">
-        <v>79254</v>
+        <v>57953</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4564,34 +4608,39 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Lappberget, Mpd</t>
+          <t>Alderbackberget, Mpd</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>601173</v>
+        <v>601240</v>
       </c>
       <c r="R38" t="n">
-        <v>6959739</v>
+        <v>6959385</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4616,34 +4665,19 @@
           <t>Ljustorp</t>
         </is>
       </c>
-      <c r="X38" t="inlineStr">
-        <is>
-          <t>2025_0530</t>
-        </is>
-      </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
-        </is>
-      </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>09:36</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
-        </is>
-      </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>09:36</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4658,26 +4692,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>David Isaksson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Måns Svensson</t>
-        </is>
-      </c>
-      <c r="AY38" t="inlineStr">
-        <is>
-          <t>Kustpaketet</t>
-        </is>
-      </c>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>131106643</v>
+        <v>129744814</v>
       </c>
       <c r="B39" t="n">
-        <v>78657</v>
+        <v>57953</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4685,43 +4715,39 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6437</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>cm²</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Lappberget, Mpd</t>
+          <t>Alderbackberget, Mpd</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>601129</v>
+        <v>601247</v>
       </c>
       <c r="R39" t="n">
-        <v>6959679</v>
+        <v>6959312</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4746,29 +4772,19 @@
           <t>Ljustorp</t>
         </is>
       </c>
-      <c r="X39" t="inlineStr">
-        <is>
-          <t>2025_0533</t>
-        </is>
-      </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
-        </is>
-      </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>09:55</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
-        </is>
-      </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>09:55</t>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4783,70 +4799,62 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>David Isaksson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Samuel Koont</t>
-        </is>
-      </c>
-      <c r="AY39" t="inlineStr">
-        <is>
-          <t>Kustpaketet</t>
-        </is>
-      </c>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>131106645</v>
+        <v>129744878</v>
       </c>
       <c r="B40" t="n">
-        <v>98944</v>
+        <v>57953</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>219790</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Lappberget, Mpd</t>
+          <t>Alderbackberget, Mpd</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>601136</v>
+        <v>601263</v>
       </c>
       <c r="R40" t="n">
-        <v>6959685</v>
+        <v>6959271</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4871,29 +4879,19 @@
           <t>Ljustorp</t>
         </is>
       </c>
-      <c r="X40" t="inlineStr">
-        <is>
-          <t>2025_0531</t>
-        </is>
-      </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
-        </is>
-      </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>09:51</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
-        </is>
-      </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>09:51</t>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4908,15 +4906,1739 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>129745588</v>
+      </c>
+      <c r="B41" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Alderbackberget, Mpd</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>601286</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6959377</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Timrå</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Ljustorp</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>129745703</v>
+      </c>
+      <c r="B42" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Alderbackberget, Mpd</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>601258</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6959417</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Timrå</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Ljustorp</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>129745723</v>
+      </c>
+      <c r="B43" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Alderbackberget, Mpd</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>601272</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6959413</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Timrå</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Ljustorp</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>129745773</v>
+      </c>
+      <c r="B44" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Alderbackberget, Mpd</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>601280</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6959438</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Timrå</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Ljustorp</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>131106659</v>
+      </c>
+      <c r="B45" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Lappberget, Mpd</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>601218</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6959810</v>
+      </c>
+      <c r="S45" t="n">
+        <v>10</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Timrå</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Ljustorp</t>
+        </is>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>2025_0517</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>08:33</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>08:33</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>På gran i barrblandskog. Ev. liten hackspett, men är med stor sannolikhet tretåig hackspett enligt diskussion med Anders Forsberg.</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
           <t>David Isaksson</t>
         </is>
       </c>
-      <c r="AX40" t="inlineStr">
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Karin Halldin</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr">
+        <is>
+          <t>Kustpaketet</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>129743173</v>
+      </c>
+      <c r="B46" t="n">
+        <v>57794</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>102621</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Sparvuggla</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Glaucidium passerinum</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Lappberget, Mpd</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>601219</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6959648</v>
+      </c>
+      <c r="S46" t="n">
+        <v>10</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Timrå</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Ljustorp</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>129744479</v>
+      </c>
+      <c r="B47" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Alderbackberget, Mpd</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>601226</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6959363</v>
+      </c>
+      <c r="S47" t="n">
+        <v>10</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Timrå</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Ljustorp</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>129744699</v>
+      </c>
+      <c r="B48" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Alderbackberget, Mpd</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>601189</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6959263</v>
+      </c>
+      <c r="S48" t="n">
+        <v>10</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Timrå</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Ljustorp</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>131106645</v>
+      </c>
+      <c r="B49" t="n">
+        <v>99035</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Lappberget, Mpd</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>601136</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6959685</v>
+      </c>
+      <c r="S49" t="n">
+        <v>10</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Timrå</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Ljustorp</t>
+        </is>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>2025_0531</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>09:51</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>09:51</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>David Isaksson</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
         <is>
           <t>Samuel Koont</t>
         </is>
       </c>
-      <c r="AY40" t="inlineStr">
+      <c r="AY49" t="inlineStr">
+        <is>
+          <t>Kustpaketet</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>112538834</v>
+      </c>
+      <c r="B50" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Stor-skälsjön, Mpd</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>601228</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6959270</v>
+      </c>
+      <c r="S50" t="n">
+        <v>10</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Timrå</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Ljustorp</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2023-09-30</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2023-09-30</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>112538844</v>
+      </c>
+      <c r="B51" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Stor-skälsjön, Mpd</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>601219</v>
+      </c>
+      <c r="R51" t="n">
+        <v>6959653</v>
+      </c>
+      <c r="S51" t="n">
+        <v>10</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Timrå</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Ljustorp</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2023-09-30</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2023-09-30</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>129744685</v>
+      </c>
+      <c r="B52" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Alderbackberget, Mpd</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>601189</v>
+      </c>
+      <c r="R52" t="n">
+        <v>6959263</v>
+      </c>
+      <c r="S52" t="n">
+        <v>10</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Timrå</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Ljustorp</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>112538855</v>
+      </c>
+      <c r="B53" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Stor-skälsjön, Mpd</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>601142</v>
+      </c>
+      <c r="R53" t="n">
+        <v>6959195</v>
+      </c>
+      <c r="S53" t="n">
+        <v>10</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Timrå</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Ljustorp</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2023-09-29</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2023-09-29</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>129743807</v>
+      </c>
+      <c r="B54" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Lappberget, Mpd</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>601219</v>
+      </c>
+      <c r="R54" t="n">
+        <v>6959554</v>
+      </c>
+      <c r="S54" t="n">
+        <v>10</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Timrå</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Ljustorp</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>131106652</v>
+      </c>
+      <c r="B55" t="n">
+        <v>80392</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Lappberget, Mpd</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>601273</v>
+      </c>
+      <c r="R55" t="n">
+        <v>6959781</v>
+      </c>
+      <c r="S55" t="n">
+        <v>10</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Timrå</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Ljustorp</t>
+        </is>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>2025_0524</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>08:52</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>08:52</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>aspstubbe</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>David Isaksson</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Måns Svensson</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr">
+        <is>
+          <t>Kustpaketet</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>131106642</v>
+      </c>
+      <c r="B56" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Lappberget, Mpd</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>601127</v>
+      </c>
+      <c r="R56" t="n">
+        <v>6959676</v>
+      </c>
+      <c r="S56" t="n">
+        <v>10</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Timrå</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Ljustorp</t>
+        </is>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>2025_0534</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>09:58</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>09:58</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>talltorraka</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>David Isaksson</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Måns Svensson</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr">
         <is>
           <t>Kustpaketet</t>
         </is>

--- a/artfynd/A 46081-2025 artfynd.xlsx
+++ b/artfynd/A 46081-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY56"/>
+  <dimension ref="A1:AZ56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112538840</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129742520</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -996,6 +1011,11 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131106656</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1121,6 +1141,11 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131106658</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1218,6 +1243,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112538841</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1315,6 +1345,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112538853</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1445,6 +1480,11 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131106649</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1542,6 +1582,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112538843</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1639,6 +1684,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112538837</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1736,6 +1786,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112538839</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1833,6 +1888,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129742766</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1930,6 +1990,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112538832</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2027,6 +2092,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112538838</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2124,6 +2194,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112538847</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2245,6 +2320,11 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131106646</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2370,6 +2450,11 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131106643</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2467,6 +2552,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112538846</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2564,6 +2654,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112538854</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2661,6 +2756,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129742454</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2786,6 +2886,11 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131106660</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2883,6 +2988,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112538842</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2980,6 +3090,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112538856</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3101,6 +3216,11 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131106648</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3231,6 +3351,11 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131106661</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3361,6 +3486,11 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131106663</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3458,6 +3588,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112538836</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3555,6 +3690,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129742486</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3680,6 +3820,11 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131106655</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3810,6 +3955,11 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131106657</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3935,6 +4085,11 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131106644</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4060,6 +4215,11 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131106662</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4167,6 +4327,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129742961</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4273,6 +4438,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129743133</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4380,6 +4550,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129744133</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4487,6 +4662,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129744201</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4594,6 +4774,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129744312</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4701,6 +4886,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129744421</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4808,6 +4998,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129744814</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4915,6 +5110,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129744878</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5022,6 +5222,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129745588</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5129,6 +5334,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129745703</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5236,6 +5446,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129745723</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5343,6 +5558,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129745773</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5464,6 +5684,11 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131106659</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5570,6 +5795,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129743173</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5672,6 +5902,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129744479</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5778,6 +6013,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129744699</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5903,6 +6143,11 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131106645</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -6000,6 +6245,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112538834</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6097,6 +6347,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112538844</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6198,6 +6453,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129744685</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6295,6 +6555,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112538855</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6392,6 +6657,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129743807</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6513,6 +6783,11 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131106652</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6643,8 +6918,70 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131106642</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>